--- a/artfynd/A 17512-2026 artfynd.xlsx
+++ b/artfynd/A 17512-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>133378282</v>
       </c>
       <c r="B2" t="n">
-        <v>91978</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,6 +791,216 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133402557</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98277</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Katrineborg VNV om , Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>591555</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6537086</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133402982</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Katrineborg VNV om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591555</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537086</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17512-2026 artfynd.xlsx
+++ b/artfynd/A 17512-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133378282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133402557</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133402982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>